--- a/Team-Data/2009-10/4-14-2009-10.xlsx
+++ b/Team-Data/2009-10/4-14-2009-10.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -679,7 +746,7 @@
         <v>38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K2" t="n">
         <v>0.467</v>
@@ -691,16 +758,16 @@
         <v>17.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O2" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P2" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R2" t="n">
         <v>11.9</v>
@@ -709,52 +776,52 @@
         <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.5</v>
+        <v>101.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
         <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>7</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
         <v>12</v>
@@ -766,13 +833,13 @@
         <v>14</v>
       </c>
       <c r="AM2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
@@ -781,28 +848,28 @@
         <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>7</v>
@@ -811,7 +878,7 @@
         <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6</v>
+        <v>0.617</v>
       </c>
       <c r="H3" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>76.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T3" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="U3" t="n">
         <v>23.5</v>
@@ -900,10 +967,10 @@
         <v>14.9</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -915,22 +982,22 @@
         <v>21.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="n">
         <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
@@ -945,13 +1012,13 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
         <v>14</v>
@@ -960,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,19 +1042,19 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
@@ -996,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1040,67 +1107,67 @@
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M4" t="n">
         <v>16.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P4" t="n">
         <v>26.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T4" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W4" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y4" t="n">
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
         <v>22</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
         <v>3</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1133,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
@@ -1142,13 +1209,13 @@
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
@@ -1160,13 +1227,13 @@
         <v>29</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1175,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
         <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.451</v>
@@ -1234,7 +1301,7 @@
         <v>4.3</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="N5" t="n">
         <v>0.33</v>
@@ -1246,16 +1313,16 @@
         <v>23.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R5" t="n">
         <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T5" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U5" t="n">
         <v>20.8</v>
@@ -1282,13 +1349,13 @@
         <v>97.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,13 +1364,13 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
@@ -1339,19 +1406,19 @@
         <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
       </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.763</v>
+        <v>0.753</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J6" t="n">
         <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.488</v>
+        <v>0.486</v>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
       <c r="R6" t="n">
         <v>9.699999999999999</v>
@@ -1437,37 +1504,37 @@
         <v>32.9</v>
       </c>
       <c r="T6" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U6" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
         <v>13.9</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
         <v>27</v>
@@ -1500,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>7</v>
@@ -1524,7 +1591,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -1536,10 +1603,10 @@
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1574,22 +1641,22 @@
         <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.679</v>
+        <v>0.667</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0.465</v>
@@ -1601,16 +1668,16 @@
         <v>18.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O7" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P7" t="n">
         <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.2</v>
@@ -1619,34 +1686,34 @@
         <v>31.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U7" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W7" t="n">
         <v>7.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
         <v>102.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
         <v>3</v>
@@ -1664,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ7" t="n">
         <v>14</v>
@@ -1679,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1691,13 +1758,13 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
         <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
         <v>3</v>
@@ -1709,7 +1776,7 @@
         <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1718,10 +1785,10 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.642</v>
+        <v>0.646</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.468</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O8" t="n">
         <v>23.6</v>
@@ -1798,7 +1865,7 @@
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
         <v>41.4</v>
@@ -1810,13 +1877,13 @@
         <v>13.9</v>
       </c>
       <c r="W8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>5.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z8" t="n">
         <v>22.5</v>
@@ -1825,16 +1892,16 @@
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.4</v>
+        <v>106.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
@@ -1843,10 +1910,10 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
         <v>17</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,13 +1937,13 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1891,10 +1958,10 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -1953,34 +2020,34 @@
         <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K9" t="n">
         <v>0.445</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="M9" t="n">
         <v>14.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P9" t="n">
         <v>24.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="R9" t="n">
         <v>12.9</v>
       </c>
       <c r="S9" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="T9" t="n">
         <v>40.2</v>
@@ -1989,10 +2056,10 @@
         <v>19.4</v>
       </c>
       <c r="V9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W9" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>3.8</v>
@@ -2007,10 +2074,10 @@
         <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.4</v>
+        <v>-5.2</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
@@ -2025,7 +2092,7 @@
         <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
@@ -2040,13 +2107,13 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN9" t="n">
         <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP9" t="n">
         <v>16</v>
@@ -2067,10 +2134,10 @@
         <v>26</v>
       </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
         <v>27</v>
@@ -2082,7 +2149,7 @@
         <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -2120,13 +2187,13 @@
         <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>0.321</v>
+        <v>0.309</v>
       </c>
       <c r="H10" t="n">
         <v>48.1</v>
@@ -2141,25 +2208,25 @@
         <v>0.469</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M10" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N10" t="n">
         <v>0.375</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P10" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R10" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>29.2</v>
@@ -2171,7 +2238,7 @@
         <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>9.300000000000001</v>
@@ -2180,34 +2247,34 @@
         <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA10" t="n">
         <v>21.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.8</v>
+        <v>108.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
         <v>3</v>
       </c>
       <c r="AE10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH10" t="n">
         <v>25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>26</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2228,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -2246,10 +2313,10 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
@@ -2264,7 +2331,7 @@
         <v>30</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>0.513</v>
+        <v>0.519</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J11" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P11" t="n">
         <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R11" t="n">
         <v>11.9</v>
       </c>
       <c r="S11" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T11" t="n">
         <v>42.1</v>
       </c>
       <c r="U11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X11" t="n">
         <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>102.5</v>
+        <v>102.2</v>
       </c>
       <c r="AC11" t="n">
         <v>-0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
@@ -2395,13 +2462,13 @@
         <v>16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK11" t="n">
         <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>4</v>
@@ -2416,25 +2483,25 @@
         <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>26</v>
@@ -2443,13 +2510,13 @@
         <v>30</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>2</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -2496,55 +2563,55 @@
         <v>48.1</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
         <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S12" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
         <v>41.5</v>
       </c>
       <c r="U12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z12" t="n">
         <v>22.5</v>
@@ -2553,10 +2620,10 @@
         <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD12" t="n">
         <v>3</v>
@@ -2571,13 +2638,13 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
@@ -2589,40 +2656,40 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>28</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>19</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>0.363</v>
+        <v>0.346</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
@@ -2690,46 +2757,46 @@
         <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="O13" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
         <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="R13" t="n">
         <v>11.3</v>
       </c>
       <c r="S13" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U13" t="n">
         <v>22</v>
       </c>
       <c r="V13" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA13" t="n">
         <v>19.4</v>
@@ -2738,37 +2805,37 @@
         <v>95.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH13" t="n">
         <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
         <v>27</v>
@@ -2786,13 +2853,13 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
         <v>28</v>
@@ -2813,7 +2880,7 @@
         <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
@@ -2875,16 +2942,16 @@
         <v>19.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
         <v>11.8</v>
@@ -2899,10 +2966,10 @@
         <v>21.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W14" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X14" t="n">
         <v>4.9</v>
@@ -2914,13 +2981,13 @@
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
         <v>3</v>
@@ -2935,16 +3002,16 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
         <v>7</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2959,13 +3026,13 @@
         <v>17</v>
       </c>
       <c r="AP14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -2974,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV14" t="n">
         <v>6</v>
@@ -2983,13 +3050,13 @@
         <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
         <v>12</v>
@@ -2998,7 +3065,7 @@
         <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3042,46 +3109,46 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="J15" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L15" t="n">
         <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="N15" t="n">
         <v>0.339</v>
       </c>
       <c r="O15" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P15" t="n">
         <v>26.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.9</v>
@@ -3093,34 +3160,34 @@
         <v>6.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.8</v>
+        <v>102.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD15" t="n">
         <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
         <v>6</v>
@@ -3138,7 +3205,7 @@
         <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
         <v>4</v>
@@ -3150,13 +3217,13 @@
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3165,10 +3232,10 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3177,7 +3244,7 @@
         <v>3</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3221,25 +3288,25 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.459</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
         <v>17.8</v>
@@ -3248,16 +3315,16 @@
         <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
         <v>31.1</v>
       </c>
       <c r="T16" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U16" t="n">
         <v>18.9</v>
@@ -3266,25 +3333,25 @@
         <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA16" t="n">
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
         <v>3</v>
@@ -3299,25 +3366,25 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>25</v>
       </c>
       <c r="AK16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN16" t="n">
         <v>19</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>21</v>
@@ -3326,37 +3393,37 @@
         <v>21</v>
       </c>
       <c r="AQ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR16" t="n">
         <v>20</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
         <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
@@ -3409,19 +3476,19 @@
         <v>37.2</v>
       </c>
       <c r="J17" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M17" t="n">
         <v>22.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O17" t="n">
         <v>15.4</v>
@@ -3430,7 +3497,7 @@
         <v>20.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R17" t="n">
         <v>11.8</v>
@@ -3445,7 +3512,7 @@
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3454,25 +3521,25 @@
         <v>4.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA17" t="n">
         <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF17" t="n">
         <v>14</v>
@@ -3493,7 +3560,7 @@
         <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM17" t="n">
         <v>5</v>
@@ -3508,7 +3575,7 @@
         <v>29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>8</v>
@@ -3517,7 +3584,7 @@
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3526,13 +3593,13 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3576,13 +3643,13 @@
         <v>81</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
-        <v>0.173</v>
+        <v>0.185</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
@@ -3591,28 +3658,28 @@
         <v>37.9</v>
       </c>
       <c r="J18" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N18" t="n">
         <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P18" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R18" t="n">
         <v>11.7</v>
@@ -3621,28 +3688,28 @@
         <v>31.2</v>
       </c>
       <c r="T18" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z18" t="n">
         <v>20.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB18" t="n">
         <v>98.2</v>
@@ -3663,16 +3730,16 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>26</v>
@@ -3690,10 +3757,10 @@
         <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>12</v>
@@ -3708,19 +3775,19 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3767,25 +3834,25 @@
         <v>0.148</v>
       </c>
       <c r="H19" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J19" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="O19" t="n">
         <v>19.1</v>
@@ -3794,7 +3861,7 @@
         <v>24.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R19" t="n">
         <v>10.9</v>
@@ -3806,7 +3873,7 @@
         <v>39.5</v>
       </c>
       <c r="U19" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V19" t="n">
         <v>14.3</v>
@@ -3815,22 +3882,22 @@
         <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA19" t="n">
         <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="AD19" t="n">
         <v>3</v>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AN19" t="n">
         <v>29</v>
@@ -3872,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3884,25 +3951,25 @@
         <v>28</v>
       </c>
       <c r="AU19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -3940,43 +4007,43 @@
         <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0.457</v>
+        <v>0.444</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="J20" t="n">
         <v>83.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O20" t="n">
         <v>15.8</v>
       </c>
       <c r="P20" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R20" t="n">
         <v>10.5</v>
@@ -3985,16 +4052,16 @@
         <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U20" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>3.7</v>
@@ -4006,13 +4073,13 @@
         <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
         <v>3</v>
@@ -4027,10 +4094,10 @@
         <v>20</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
         <v>9</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4054,31 +4121,31 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>30</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
@@ -4087,7 +4154,7 @@
         <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -4134,37 +4201,37 @@
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J21" t="n">
         <v>83.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O21" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P21" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0.782</v>
       </c>
       <c r="R21" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S21" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T21" t="n">
         <v>40.4</v>
@@ -4176,10 +4243,10 @@
         <v>14</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4.5</v>
@@ -4191,7 +4258,7 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AC21" t="n">
         <v>-3.6</v>
@@ -4203,10 +4270,10 @@
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>5</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
         <v>26</v>
@@ -4239,13 +4306,13 @@
         <v>5</v>
       </c>
       <c r="AR21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU21" t="n">
         <v>13</v>
@@ -4257,19 +4324,19 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
         <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -4325,16 +4392,16 @@
         <v>0.461</v>
       </c>
       <c r="L22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O22" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P22" t="n">
         <v>27</v>
@@ -4343,7 +4410,7 @@
         <v>0.805</v>
       </c>
       <c r="R22" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S22" t="n">
         <v>31.8</v>
@@ -4352,7 +4419,7 @@
         <v>43.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V22" t="n">
         <v>15</v>
@@ -4361,19 +4428,19 @@
         <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y22" t="n">
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC22" t="n">
         <v>3.4</v>
@@ -4382,13 +4449,13 @@
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4406,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="AM22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN22" t="n">
         <v>26</v>
@@ -4427,7 +4494,7 @@
         <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
@@ -4442,19 +4509,19 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB22" t="n">
         <v>15</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>13</v>
-      </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -4504,22 +4571,22 @@
         <v>77.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P23" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0.723</v>
@@ -4534,10 +4601,10 @@
         <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
         <v>6.3</v>
@@ -4573,10 +4640,10 @@
         <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>28</v>
@@ -4591,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4618,10 +4685,10 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
@@ -4633,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC23" t="n">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4762,7 @@
         <v>16.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
@@ -4704,7 +4771,7 @@
         <v>22</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R24" t="n">
         <v>11.5</v>
@@ -4722,16 +4789,16 @@
         <v>14.6</v>
       </c>
       <c r="W24" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA24" t="n">
         <v>18.7</v>
@@ -4758,7 +4825,7 @@
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
@@ -4770,7 +4837,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="n">
         <v>22</v>
@@ -4782,7 +4849,7 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
         <v>11</v>
@@ -4806,7 +4873,7 @@
         <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
         <v>14</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -4862,10 +4929,10 @@
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="J25" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.492</v>
@@ -4874,10 +4941,10 @@
         <v>8.9</v>
       </c>
       <c r="M25" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
       <c r="O25" t="n">
         <v>19.9</v>
@@ -4892,13 +4959,13 @@
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U25" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V25" t="n">
         <v>14.8</v>
@@ -4907,10 +4974,10 @@
         <v>5.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z25" t="n">
         <v>20.9</v>
@@ -4919,10 +4986,10 @@
         <v>21.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>110.2</v>
+        <v>110.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD25" t="n">
         <v>3</v>
@@ -4937,7 +5004,7 @@
         <v>5</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4946,7 +5013,7 @@
         <v>13</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4958,10 +5025,10 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>11</v>
@@ -4970,7 +5037,7 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
         <v>6</v>
@@ -4979,19 +5046,19 @@
         <v>4</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>29</v>
       </c>
       <c r="AX25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY25" t="n">
         <v>12</v>
       </c>
-      <c r="AY25" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5000,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="BC25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5032,34 +5099,34 @@
         <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.605</v>
+        <v>0.617</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
         <v>5.9</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O26" t="n">
         <v>19.6</v>
@@ -5068,43 +5135,43 @@
         <v>24.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T26" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W26" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
         <v>3</v>
@@ -5119,10 +5186,10 @@
         <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ26" t="n">
         <v>26</v>
@@ -5134,13 +5201,13 @@
         <v>18</v>
       </c>
       <c r="AM26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="n">
         <v>14</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
@@ -5170,10 +5237,10 @@
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
         <v>9</v>
@@ -5182,7 +5249,7 @@
         <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" t="n">
-        <v>0.309</v>
+        <v>0.305</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J27" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L27" t="n">
         <v>5.9</v>
@@ -5241,7 +5308,7 @@
         <v>16.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O27" t="n">
         <v>17.4</v>
@@ -5250,19 +5317,19 @@
         <v>24</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T27" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V27" t="n">
         <v>15</v>
@@ -5283,43 +5350,43 @@
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
         <v>5</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>19</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>25</v>
@@ -5343,10 +5410,10 @@
         <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>23</v>
@@ -5358,10 +5425,10 @@
         <v>26</v>
       </c>
       <c r="BA27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5396,34 +5463,34 @@
         <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G28" t="n">
-        <v>0.605</v>
+        <v>0.617</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J28" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.472</v>
+        <v>0.474</v>
       </c>
       <c r="L28" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M28" t="n">
         <v>18.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="O28" t="n">
         <v>17.8</v>
@@ -5438,16 +5505,16 @@
         <v>10.8</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T28" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V28" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W28" t="n">
         <v>6.3</v>
@@ -5459,16 +5526,16 @@
         <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.2</v>
+        <v>101.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AD28" t="n">
         <v>3</v>
@@ -5483,10 +5550,10 @@
         <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5495,46 +5562,46 @@
         <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>11</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO28" t="n">
         <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>13</v>
@@ -5543,7 +5610,7 @@
         <v>19</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5590,43 +5657,43 @@
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="J29" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.483</v>
+        <v>0.48</v>
       </c>
       <c r="L29" t="n">
         <v>6.3</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R29" t="n">
         <v>9.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="U29" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
         <v>13.4</v>
@@ -5641,16 +5708,16 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.1</v>
+        <v>103.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD29" t="n">
         <v>3</v>
@@ -5665,7 +5732,7 @@
         <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
@@ -5686,40 +5753,40 @@
         <v>6</v>
       </c>
       <c r="AO29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP29" t="n">
         <v>8</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5772,31 +5839,31 @@
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J30" t="n">
         <v>80.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="P30" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R30" t="n">
         <v>10.6</v>
@@ -5808,10 +5875,10 @@
         <v>42.2</v>
       </c>
       <c r="U30" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
@@ -5823,16 +5890,16 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.2</v>
+        <v>104.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD30" t="n">
         <v>3</v>
@@ -5847,16 +5914,16 @@
         <v>5</v>
       </c>
       <c r="AH30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ30" t="n">
         <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS30" t="n">
         <v>9</v>
@@ -5895,10 +5962,10 @@
         <v>4</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6024,7 @@
         <v>36.7</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.449</v>
@@ -5966,10 +6033,10 @@
         <v>5.3</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O31" t="n">
         <v>17.6</v>
@@ -5978,7 +6045,7 @@
         <v>23.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
@@ -5993,7 +6060,7 @@
         <v>19</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W31" t="n">
         <v>6</v>
@@ -6002,7 +6069,7 @@
         <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
         <v>21.3</v>
@@ -6014,37 +6081,37 @@
         <v>96.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD31" t="n">
         <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>23</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>24</v>
       </c>
       <c r="AM31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN31" t="n">
         <v>13</v>
@@ -6062,7 +6129,7 @@
         <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>17</v>
@@ -6071,7 +6138,7 @@
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>28</v>
@@ -6080,13 +6147,13 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA31" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-14-2009-10</t>
+          <t>2010-04-14</t>
         </is>
       </c>
     </row>
